--- a/validation_2010_age8/edge_validation.xlsx
+++ b/validation_2010_age8/edge_validation.xlsx
@@ -442,17 +442,19 @@
       </c>
       <c r="G8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The added nutritional review abstract describes topics and the need to scrutinize study validity, but reports no treatment-effect conclusion. It cannot validate better general nutrition reducing ADHD symptom severity.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Obtain the full review or directly relevant nutritional-intervention results; keep general nutrition separate from individual supplements or elimination diets.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21766545: This updated review presents the evidence regarding the usefulness and limitations of the most frequent nutritional and dietary interventions in the treatment of ADHD and/or ASD.
+Location: Effectiveness of nutritional interventions on the functioning of children with ADHD and_or ASD. An updated review of research evidence - PubMed.html; article abstract (#eng-abstract)
+Relevance: Abstract describes the review scope but supplies no efficacy conclusion, effect size or comparison supporting the direction of the nutrition edge.</t>
         </is>
       </c>
     </row>
@@ -489,12 +491,12 @@
       </c>
       <c r="G9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">At ages 7-8, shorter objectively measured sleep was associated with more inattentive/hyperactive behavior. The paper emphasizes that most evidence is correlational.</t>
+          <t xml:space="preserve">The existing actigraphy-duration association near ages seven–eight remains relevant. The added study finds parent-reported sleep problems associated with behavior but no polysomnographic group differences. It strengthens measurement and direction cautions rather than establishing a causal sleep-to-severity effect.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain a qualified negative pathway from sleep duration or quality to behavior and label causal direction uncertain.</t>
+          <t xml:space="preserve">Keep the qualified sleep association; identify the sleep measure, informant and uncertain direction. Do not label different sleep measures as contradictory tests of one causal intervention.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr" s="0">
@@ -504,7 +506,13 @@
 Relevance: Directly relevant to age eight, but observational wording supports association rather than a fully identified causal effect.
 SLEEP_BEHAVIOR: There is some evidence of a causal relationship between sleep disruption and difficulties regulating behavior, emotion, and attention. However, such associations have rarely been experimentally evaluated, because the majority of sleep studies have used correlational designs.
 Location: PDF page 2
-Relevance: The review itself states both the plausible direction and the causal limitation.</t>
+Relevance: The review itself states both the plausible direction and the causal limitation.
+PMID_21206548: However, there were no differences between ADHD and healthy groups on any polysomnographic variables, including sleep structure, arousals, and respiratory disturbances.
+Location: Differences between objective and subjective sleep measures in children with attention deficit hyperactivity disorder - PubMed.html; article abstract (#eng-abstract)
+Relevance: Unmedicated children aged 7–12; objective group comparisons differed from parental sleep reports. No intervention on sleep or causal severity effect.
+PMID_21206548: Reported sleep problems were significantly associated with almost all subscales of CBCL as well as CBCL total score.
+Location: Differences between objective and subjective sleep measures in children with attention deficit hyperactivity disorder - PubMed.html; article abstract (#eng-abstract)
+Relevance: Subjective sleep-behavior association; shared informant effects and reverse direction remain possible. This does not negate the earlier actigraphy-duration association.</t>
         </is>
       </c>
     </row>
@@ -541,19 +549,22 @@
       </c>
       <c r="G10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">A cohort study found prenatal organochlorine exposure associated with ADHD-like behaviors. This supports one specified exposure, not generic environmental stressors.</t>
+          <t xml:space="preserve">The existing prenatal organochlorine association is supplemented by lifetime lead associated with recorded pediatric ADHD diagnosis. Both are exposure-specific observational evidence, not generic stressor effects on severity.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Replace Environmental Exposure with the measured prenatal contaminant construct or keep the generic edge explicitly provisional.</t>
+          <t xml:space="preserve">Specify contaminant, timing and endpoint; retain confounding and ascertainment limitations.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">ORGANOCHLORINE: These results support an association between low-level prenatal organochlorine exposure and ADHD-like behaviors in childhood.
 Location: PDF page 1
-Relevance: Supports a specific prenatal exposure association, narrower than the graph's generic environmental-stressor claim.</t>
+Relevance: Supports a specific prenatal exposure association, narrower than the graph's generic environmental-stressor claim.
+PMID_21391408: elevated lead remained a significant predictor of ADHD diagnosis in multivariate analysis.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Lifetime lead association with recorded pediatric diagnosis; not proof of generic environmental stressor effects on symptom severity.</t>
         </is>
       </c>
     </row>
@@ -590,19 +601,22 @@
       </c>
       <c r="G11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The corpus consistently links ADHD symptoms with functional impairment, but the supplied wording does not identify an independent causal severity gradient.</t>
+          <t xml:space="preserve">Existing ADHD–impairment context is supplemented by psychosocial/educational problems in a selected Tourette sample with ADHD/OCD comorbidity. The new association does not identify an independent symptom-severity causal gradient.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain as a clinically coherent pathway while distinguishing definitional association from causal effect.</t>
+          <t xml:space="preserve">Keep population-specific functional context separate from a causal severity effect.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">ODD_REVIEW: Attention-deficit/hyperactivity disorder (ADHD) is a highly prevalent disorder with significant functional impairment.
 Location: PDF page 1
-Relevance: Links ADHD and impairment, but does not independently estimate symptom-severity-to-impairment causation.</t>
+Relevance: Links ADHD and impairment, but does not independently estimate symptom-severity-to-impairment causation.
+PMID_19482837: A higher rate of these problems was also seen if the comorbidities attention-deficit hyperactivity disorder (ADHD) and/or obsessive compulsive disorder were present.
+Location: The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome - PubMed.html; article abstract (#eng-abstract)
+Relevance: Selected Tourette pediatric sample: psychosocial and educational problems correlate with comorbidity; school support need is not evidence that ADHD diagnosis causes formal accommodations.</t>
         </is>
       </c>
     </row>
@@ -686,17 +700,22 @@
       </c>
       <c r="G13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The geographic study shows differences in recorded pediatric diagnoses, and the commentary proposes access/referral contributors. Neither measures this specific graph exposure-to-outcome effect; geographic or racial diagnosis differences alone do not establish provider availability, institutional bias, or referral causation.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as unvalidated; measure the named exposure and endpoint directly rather than substituting recorded diagnosis distribution.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1104,22 +1123,27 @@
       </c>
       <c r="F22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The pediatric disparity commentary relates diagnosis/treatment distribution to socioeconomic circumstances and proposes insurance/service barriers. This supports only a narrower socioeconomic care-inequity pathway; it does not measure SES causing access to evaluation at age eight.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as a qualified care-disparity pathway; separate underlying prevalence, recorded diagnosis, insurance and actual service access.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391409: This adds additional evidence that trends in the diagnosis and treatment for ADHD in children move in the exact opposite direction from those who are at highest risk for meeting criteria, for experiencing impairment, for and downstream socioeconomic sequelae.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Pediatric disparity commentary: diagnosis/treatment distribution across socioeconomic groups, not a controlled effect of SES on access or continuity. Geography, prevalence and ascertainment remain confounded.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1151,22 +1175,24 @@
       </c>
       <c r="F23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The pediatric commentary identifies inadequate insurance coverage as a possible contributor to diagnostic and treatment problems. This supplies clinical support for a financial-access barrier, but does not measure household income, affordability or a controlled age-eight access effect.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Specify insurance/affordability as the proposed barrier and retain uncertainty about magnitude and causal direction.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1229,22 @@
       </c>
       <c r="G24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The geographic study shows differences in recorded pediatric diagnoses, and the commentary proposes access/referral contributors. Neither measures this specific graph exposure-to-outcome effect; geographic or racial diagnosis differences alone do not establish provider availability, institutional bias, or referral causation.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as unvalidated; measure the named exposure and endpoint directly rather than substituting recorded diagnosis distribution.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1281,22 @@
       </c>
       <c r="G25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The geographic study shows differences in recorded pediatric diagnoses, and the commentary proposes access/referral contributors. Neither measures this specific graph exposure-to-outcome effect; geographic or racial diagnosis differences alone do not establish provider availability, institutional bias, or referral causation.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as unvalidated; measure the named exposure and endpoint directly rather than substituting recorded diagnosis distribution.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1344,17 +1380,22 @@
       </c>
       <c r="G27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The geographic study shows differences in recorded pediatric diagnoses, and the commentary proposes access/referral contributors. Neither measures this specific graph exposure-to-outcome effect; geographic or racial diagnosis differences alone do not establish provider availability, institutional bias, or referral causation.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as unvalidated; measure the named exposure and endpoint directly rather than substituting recorded diagnosis distribution.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1532,17 +1573,22 @@
       </c>
       <c r="G31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The geographic study shows differences in recorded pediatric diagnoses, and the commentary proposes access/referral contributors. Neither measures this specific graph exposure-to-outcome effect; geographic or racial diagnosis differences alone do not establish provider availability, institutional bias, or referral causation.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as unvalidated; measure the named exposure and endpoint directly rather than substituting recorded diagnosis distribution.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1579,17 +1625,22 @@
       </c>
       <c r="G32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The geographic study shows differences in recorded pediatric diagnoses, and the commentary proposes access/referral contributors. Neither measures this specific graph exposure-to-outcome effect; geographic or racial diagnosis differences alone do not establish provider availability, institutional bias, or referral causation.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as unvalidated; measure the named exposure and endpoint directly rather than substituting recorded diagnosis distribution.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -1626,17 +1677,19 @@
       </c>
       <c r="G33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Diagnosis Status is ambiguous between any diagnosis and accurate diagnosis, while Misdiagnosis Rate is an aggregate rate.</t>
+          <t xml:space="preserve">The pediatric screening study finds similar detection between two instruments, not diagnostic error against a gold standard. It does not resolve the aggregate misdiagnosis-rate versus individual accurate-diagnosis coding problem.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Define accurate diagnosis as the outcome before assigning a negative effect.</t>
+          <t xml:space="preserve">Define accurate diagnosis and an appropriate error denominator before assigning a signed causal effect.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_20200839: Conclusions: Our findings show that, in our population, there is no difference between the QLSA-ADHD and the DSM-IV for detecting ADHD.
+Location: [Population-based diagnostic study to compare the DSM-IV and the Questionnaire for screening Latin American schoolchildren and adolescents for attention deficit hyperactivity disorder] - PubMed.html; article abstract (#eng-abstract)
+Relevance: Single pediatric outpatient comparison, ages 4–14. Similar screening yield does not identify sensitivity, specificity, errors against a gold standard, or adult diagnostic variability.</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1820,7 @@
       </c>
       <c r="G36" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Guidelines connect structured diagnosis with consideration of medication, but recommendations do not establish how often diagnosis causes medication use.</t>
+          <t xml:space="preserve">Guidelines connect structured diagnosis with consideration of medication, but recommendations do not establish how often diagnosis causes medication use. The added ADHD/ODD review further supports condition-specific assessment and care recommendations, not a controlled estimate for this generic edge. </t>
         </is>
       </c>
       <c r="H36" t="inlineStr" s="0">
@@ -1779,7 +1832,10 @@
         <is>
           <t xml:space="preserve">CPG_REVIEW: The CPGs all recommend: a structured approach to diagnosis and treatment; attention to psychiatric comorbidity and other ADHD-related conflicts during an individual's lifespan; consideration of medication (usually stimulants) and psychosocial therapies; and follow-up and monitoring of patient response.
 Location: PDF page 2
-Relevance: Supports diagnosis-linked consideration of medication and psychosocial care, but does not estimate the graph's causal probabilities.</t>
+Relevance: Supports diagnosis-linked consideration of medication and psychosocial care, but does not estimate the graph's causal probabilities.
+PMID_21117844: Treatment requires management of the core symptoms of ADHD plus, in many cases, augmentation with other treatment to address the ODD.
+Location: Review of attention-deficit_hyperactivity disorder comorbid with oppositional defiant disorder - PubMed.html; article abstract (#eng-abstract)
+Relevance: Practitioner review supports condition-specific comorbidity assessment and treatment, without estimating population-level uptake or a universal therapy effect.</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1872,7 @@
       </c>
       <c r="G37" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Guidelines connect diagnosis and treatment with consideration of psychosocial therapies, without isolating diagnosis as the causal driver of uptake.</t>
+          <t xml:space="preserve">Guidelines connect diagnosis and treatment with consideration of psychosocial therapies, without isolating diagnosis as the causal driver of uptake. The added ADHD/ODD review further supports condition-specific assessment and care recommendations, not a controlled estimate for this generic edge. </t>
         </is>
       </c>
       <c r="H37" t="inlineStr" s="0">
@@ -1831,7 +1887,10 @@
 Relevance: Supports diagnosis-linked consideration of medication and psychosocial care, but does not estimate the graph's causal probabilities.
 CPG_REVIEW: consideration of medication (usually stimulants) and psychosocial therapies; and follow-up and monitoring of patient response.
 Location: PDF page 2
-Relevance: Supports psychosocial therapy as recommended care, not a quantified effect on every symptom or impairment outcome.</t>
+Relevance: Supports psychosocial therapy as recommended care, not a quantified effect on every symptom or impairment outcome.
+PMID_21117844: Treatment requires management of the core symptoms of ADHD plus, in many cases, augmentation with other treatment to address the ODD.
+Location: Review of attention-deficit_hyperactivity disorder comorbid with oppositional defiant disorder - PubMed.html; article abstract (#eng-abstract)
+Relevance: Practitioner review supports condition-specific comorbidity assessment and treatment, without estimating population-level uptake or a universal therapy effect.</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1927,19 @@
       </c>
       <c r="G38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The Tourette study reports educational support needs and problems with ADHD/OCD comorbidity, but does not measure ADHD diagnosis causing accommodations/support plans or accommodations reducing impairment.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Distinguish support need from actual support delivery and intervention benefit.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_19482837: A higher rate of these problems was also seen if the comorbidities attention-deficit hyperactivity disorder (ADHD) and/or obsessive compulsive disorder were present.
+Location: The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome - PubMed.html; article abstract (#eng-abstract)
+Relevance: Selected Tourette pediatric sample: psychosocial and educational problems correlate with comorbidity; school support need is not evidence that ADHD diagnosis causes formal accommodations.</t>
         </is>
       </c>
     </row>
@@ -1962,17 +2023,22 @@
       </c>
       <c r="G40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The geographic study shows differences in recorded pediatric diagnoses, and the commentary proposes access/referral contributors. Neither measures this specific graph exposure-to-outcome effect; geographic or racial diagnosis differences alone do not establish provider availability, institutional bias, or referral causation.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Retain as unvalidated; measure the named exposure and endpoint directly rather than substituting recorded diagnosis distribution.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391408: Conclusions: Further studies are needed to determine if geographic distribution of ADHD diagnosis can be partially explained by differential efficiency of referral for diagnosis by school districts, by race/ethnicity, and/or built environment.
+Location: Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html; article abstract (#eng-abstract)
+Relevance: Observational children aged 5–17; diagnosis differences do not identify institutional bias, provider access or school-referral efficiency as the causal mechanism.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -2004,22 +2070,27 @@
       </c>
       <c r="F41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">insufficient_evidence</t>
+          <t xml:space="preserve">partially_supported</t>
         </is>
       </c>
       <c r="G41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The commentary describes socioeconomic disparities in pediatric diagnosis and treatment. This supports uneven treatment provision, but does not demonstrate that higher SES causes treatment continuity or establish an age-eight-specific effect.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Restrict evidence to treatment-distribution disparities; obtain longitudinal continuity data before asserting that part of the reasoning.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_21391409: This adds additional evidence that trends in the diagnosis and treatment for ADHD in children move in the exact opposite direction from those who are at highest risk for meeting criteria, for experiencing impairment, for and downstream socioeconomic sequelae.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Pediatric disparity commentary: diagnosis/treatment distribution across socioeconomic groups, not a controlled effect of SES on access or continuity. Geography, prevalence and ascertainment remain confounded.
+PMID_21391409: Contributing factors, such as marginal diagnoses (such as when parent and teacher symptom reports diverge), inadequate insurance coverage, limited time, and lack of familiarity and comfort with diagnostic and prescribing guidelines, may leave the door open to misdiagnosis and treatment.
+Location: Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html; article abstract (#eng-abstract)
+Relevance: Proposed financial/service barriers in pediatric commentary, not a measured income intervention or independent access-effect estimate.</t>
         </is>
       </c>
     </row>
@@ -2244,19 +2315,22 @@
       </c>
       <c r="G46" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The pharmacotherapy review describes controlled methylphenidate efficacy studies, including children, but the quoted evidence is from a narrower developmental-disorder population and does not justify the graph's generic magnitude.</t>
+          <t xml:space="preserve">The new review summarizes randomized stimulant efficacy across childhood and adulthood, strengthening the prior efficacy evidence. It gives no separate age-eight estimate, broad drug magnitude, or universal symptom response.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain the negative edge, identify medication and population, and remove the unvalidated strength claim.</t>
+          <t xml:space="preserve">Retain stimulant-specific negative direction with age/outcome limits; numeric strength remains unvalidated.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">PHARM_REVIEW: The effectiveness of three doses of methylphenidate (0.15, 0.3, and 0.6 mg kg-1, administered twice daily) compared to placebo was investigated by Pearson et al. [2003] in a double-blind, placebo-controlled crossover study.
 Location: PDF page 2
-Relevance: Identifies controlled efficacy evidence in a narrower developmental-disorder population.</t>
+Relevance: Identifies controlled efficacy evidence in a narrower developmental-disorder population.
+PMID_20513225: Randomised controlled trials confirm that stimulant medication is efficacious for, and well tolerated by, males and females and patients across the age range; although preschoolers appear to have a less beneficial response and more side effects.
+Location: Stimulant drug effects on attention deficit_hyperactivity disorder_ a review of the effects of age and sex of patients - PubMed.html; article abstract (#eng-abstract)
+Relevance: Review of controlled stimulant trials including adulthood; broad age coverage without an estimate at exactly eight, 32 or 45. Tolerability does not mean no adverse effects.</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2367,7 @@
       </c>
       <c r="G47" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Clinical guidelines recommend psychosocial therapies, but the corpus excerpt does not establish a uniform reduction in core symptom severity across behavioral interventions.</t>
+          <t xml:space="preserve">Clinical guidelines recommend psychosocial therapies, but the corpus excerpt does not establish a uniform reduction in core symptom severity across behavioral interventions. The added ADHD/ODD review further supports condition-specific assessment and care recommendations, not a controlled estimate for this generic edge. </t>
         </is>
       </c>
       <c r="H47" t="inlineStr" s="0">
@@ -2305,7 +2379,10 @@
         <is>
           <t xml:space="preserve">CPG_REVIEW: consideration of medication (usually stimulants) and psychosocial therapies; and follow-up and monitoring of patient response.
 Location: PDF page 2
-Relevance: Supports psychosocial therapy as recommended care, not a quantified effect on every symptom or impairment outcome.</t>
+Relevance: Supports psychosocial therapy as recommended care, not a quantified effect on every symptom or impairment outcome.
+PMID_21117844: Treatment requires management of the core symptoms of ADHD plus, in many cases, augmentation with other treatment to address the ODD.
+Location: Review of attention-deficit_hyperactivity disorder comorbid with oppositional defiant disorder - PubMed.html; article abstract (#eng-abstract)
+Relevance: Practitioner review supports condition-specific comorbidity assessment and treatment, without estimating population-level uptake or a universal therapy effect.</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2419,7 @@
       </c>
       <c r="G48" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Psychosocial treatment is recommended and functional outcomes are clinically central, but this corpus does not directly estimate a generic therapy-to-impairment effect.</t>
+          <t xml:space="preserve">Psychosocial treatment is recommended and functional outcomes are clinically central, but this corpus does not directly estimate a generic therapy-to-impairment effect. The added ADHD/ODD review further supports condition-specific assessment and care recommendations, not a controlled estimate for this generic edge. </t>
         </is>
       </c>
       <c r="H48" t="inlineStr" s="0">
@@ -2357,7 +2434,10 @@
 Relevance: Supports psychosocial therapy as recommended care, not a quantified effect on every symptom or impairment outcome.
 ODD_REVIEW: Attention-deficit/hyperactivity disorder (ADHD) is a highly prevalent disorder with significant functional impairment.
 Location: PDF page 1
-Relevance: Links ADHD and impairment, but does not independently estimate symptom-severity-to-impairment causation.</t>
+Relevance: Links ADHD and impairment, but does not independently estimate symptom-severity-to-impairment causation.
+PMID_21117844: Treatment requires management of the core symptoms of ADHD plus, in many cases, augmentation with other treatment to address the ODD.
+Location: Review of attention-deficit_hyperactivity disorder comorbid with oppositional defiant disorder - PubMed.html; article abstract (#eng-abstract)
+Relevance: Practitioner review supports condition-specific comorbidity assessment and treatment, without estimating population-level uptake or a universal therapy effect.</t>
         </is>
       </c>
     </row>
@@ -2394,17 +2474,19 @@
       </c>
       <c r="G49" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The Tourette study reports educational support needs and problems with ADHD/OCD comorbidity, but does not measure ADHD diagnosis causing accommodations/support plans or accommodations reducing impairment.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Distinguish support need from actual support delivery and intervention benefit.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_19482837: A higher rate of these problems was also seen if the comorbidities attention-deficit hyperactivity disorder (ADHD) and/or obsessive compulsive disorder were present.
+Location: The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome - PubMed.html; article abstract (#eng-abstract)
+Relevance: Selected Tourette pediatric sample: psychosocial and educational problems correlate with comorbidity; school support need is not evidence that ADHD diagnosis causes formal accommodations.</t>
         </is>
       </c>
     </row>
@@ -2682,19 +2764,22 @@
       </c>
       <c r="G55" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Adverse effects are documented, but their separate causal effect on quality of life is not estimated in the supplied studies.</t>
+          <t xml:space="preserve">The medication review reports QOL improvement with treatment. This does not isolate side effects lowering QOL or receiving a diagnosis improving QOL; treatment and diagnosis are different exposures.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Obtain a study measuring adverse effects and quality of life longitudinally.</t>
+          <t xml:space="preserve">Keep the named causal claim unvalidated; model medication-related QOL benefit through a separately specified pathway.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">PHARM_REVIEW: significant adverse events such as severe social withdrawal, increased crying, drowsiness, and irritability were noted, especially at the higher dose (0.6 mg kg-1) of methylphenidate
 Location: PDF page 2
-Relevance: Directly supports medication causing adverse effects, although the population and drug are specific.</t>
+Relevance: Directly supports medication causing adverse effects, although the population and drug are specific.
+PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.</t>
         </is>
       </c>
     </row>
@@ -2731,17 +2816,19 @@
       </c>
       <c r="G56" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No supplied 2010 paper directly establishes this edge's direction, sign, and stated mechanism for children aged approximately eight. Related context is not treated as causal validation.</t>
+          <t xml:space="preserve">The Tourette study reports educational support needs and problems with ADHD/OCD comorbidity, but does not measure ADHD diagnosis causing accommodations/support plans or accommodations reducing impairment.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain only as an explicitly unvalidated hypothesis or add directly relevant evidence with a defined exposure, outcome, and temporal direction.</t>
+          <t xml:space="preserve">Distinguish support need from actual support delivery and intervention benefit.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">No directly relevant excerpt used</t>
+          <t xml:space="preserve">PMID_19482837: A higher rate of these problems was also seen if the comorbidities attention-deficit hyperactivity disorder (ADHD) and/or obsessive compulsive disorder were present.
+Location: The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome - PubMed.html; article abstract (#eng-abstract)
+Relevance: Selected Tourette pediatric sample: psychosocial and educational problems correlate with comorbidity; school support need is not evidence that ADHD diagnosis causes formal accommodations.</t>
         </is>
       </c>
     </row>
@@ -2825,19 +2912,22 @@
       </c>
       <c r="G58" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The corpus links ADHD-related psychosocial maladaptation and impairment with poorer quality of life, but does not isolate functional impairment as a causal exposure.</t>
+          <t xml:space="preserve">The corpus links ADHD-related impairment to poorer QOL. The new medication review reports QOL benefits and treats QOL as functioning-related, but does not isolate functional impairment as an independent causal exposure.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Retain as a qualified clinical pathway and seek longitudinal evidence separating symptoms, impairment, and quality of life.</t>
+          <t xml:space="preserve">Retain a qualified impairment–QOL pathway and keep treatment efficacy distinct from this edge.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">ECZEMA_SLEEP: ADHD affects more than 5% of all children and causes severe psychosocial maladaptation, impairment of quality of life and economic burden on social services.
 Location: PDF page 1
-Relevance: Supports an adverse relation between ADHD-related impairment and quality of life, but not the graph's separate diagnosis benefit.</t>
+Relevance: Supports an adverse relation between ADHD-related impairment and quality of life, but not the graph's separate diagnosis benefit.
+PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.</t>
         </is>
       </c>
     </row>
@@ -2874,19 +2964,22 @@
       </c>
       <c r="G59" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">The evidence documents impaired quality of life among diagnosed or treated children; it does not show that receiving a diagnosis itself improves quality of life.</t>
+          <t xml:space="preserve">The medication review reports QOL improvement with treatment. This does not isolate side effects lowering QOL or receiving a diagnosis improving QOL; treatment and diagnosis are different exposures.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Model mediated pathways through effective support and treatment rather than a direct diagnosis benefit.</t>
+          <t xml:space="preserve">Keep the named causal claim unvalidated; model medication-related QOL benefit through a separately specified pathway.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">ECZEMA_SLEEP: ADHD affects more than 5% of all children and causes severe psychosocial maladaptation, impairment of quality of life and economic burden on social services.
 Location: PDF page 1
-Relevance: Supports an adverse relation between ADHD-related impairment and quality of life, but not the graph's separate diagnosis benefit.</t>
+Relevance: Supports an adverse relation between ADHD-related impairment and quality of life, but not the graph's separate diagnosis benefit.
+PMID_20839896: These studies support a positive short-term effect of medication on QOL in ADHD for children, adolescents and adults that mirrors, to some extent, the effects of these medications on ADHD symptoms, although with smaller effect sizes.
+Location: The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html; article abstract (#eng-abstract)
+Relevance: Systematic review of 25 studies, mainly pediatric and atomoxetine; adult evidence limited. QOL is a related but different endpoint from separately measured functional impairment; no diagnosis-only or adverse-effect-only effect is identified.</t>
         </is>
       </c>
     </row>
@@ -2917,7 +3010,7 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Local PDF</t>
+          <t xml:space="preserve">Local file (PDF or HTML)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
@@ -3454,8 +3547,382 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="110" customHeight="1">
+      <c r="A26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20925475</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">An 'integrative neuroscience' perspective on ADHD: linking cognition, emotion, brain and genetic measures with implications for clinical support</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/An 'integrative neuroscience' perspective on ADHD_ linking cognition, emotion, brain and genetic measures with implications for clinical support - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">61ac7c7b449a4a20c8d861940094c70f183652541b56724074603e65118f0ce7</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="110" customHeight="1">
+      <c r="A27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_19270267</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Attention deficit hyperactivity disorder in men and women newly committed to prison: clinical characteristics, psychiatric comorbidity, and quality of life</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Attention deficit hyperactivity disorder in men and women newly committed to prison_ clinical characteristics, psychiatric comorbidity, and quality of life - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">4c226bb161f56d22bb25961dde6761f45708dbca6c9dc6a5bff821d73be84891</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="110" customHeight="1">
+      <c r="A28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">BIPOLAR_ADULT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Bipolar Symptoms in Adult Attention-Deficit/Hyperactivity Disorder: A Cross-Sectional Study of 510 Clinically Diagnosed Patients and 417 Population-Based Controls</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Bipolar Symptoms in Adult Attention-Deficit_Hyperactivity Disorder_ A Cross-Sectional Study of 510 Clinically Diagnosed Patients and 417 Population-Based Controls.html</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">21d9c13db53d1092a85357c530bdb1c7f62cecedce78f88f9b5fb2ad3432562b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="110" customHeight="1">
+      <c r="A29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20441004</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Can we prevent smoking in children with ADHD: a review of the literature</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Can we prevent smoking in children with ADHD_ a review of the literature - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">5b481cac24cb1945734201bb073efc838f242fec53f2934f6781b315410287ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="110" customHeight="1">
+      <c r="A30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21206548</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Differences between objective and subjective sleep measures in children with attention deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Differences between objective and subjective sleep measures in children with attention deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">095419b3ac09ece0274c7eb2a752716dbeec8a10f5de279991d2408d6cf40aa0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="110" customHeight="1">
+      <c r="A31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21391409</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Disparities in ADHD assessment, diagnosis, and treatment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Disparities in ADHD assessment, diagnosis, and treatment - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">e4e39817aefdaebc682ac29916b806dc29215c79ec3b5c582d874706267abc89</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="110" customHeight="1">
+      <c r="A32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21766545</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Effectiveness of nutritional interventions on the functioning of children with ADHD and/or ASD. An updated review of research evidence</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Effectiveness of nutritional interventions on the functioning of children with ADHD and_or ASD. An updated review of research evidence - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">a251eaa1514ee85183cd7fe767e1c822c7635da0ede4aacc84521d76b508b6e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="110" customHeight="1">
+      <c r="A33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21391408</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Geographic analysis of diagnosis of Attention-Deficit/Hyperactivity Disorder in children: Eastern Wisconsin, USA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Geographic analysis of diagnosis of Attention-Deficit_Hyperactivity Disorder in children_ Eastern Wisconsin, USA - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0039a79c3ff8ab7b5133aa240506d5bbad62bf2c41a1646b8efc827488ec2c06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="110" customHeight="1">
+      <c r="A34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20218799</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Neurochemical alterations in women with borderline personality disorder and comorbid attention-deficit hyperactivity disorder</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Neurochemical alterations in women with borderline personality disorder and comorbid attention-deficit hyperactivity disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">fa565ec4b65455fcc706729635a875ad56147454b44f6fb5d32e2b0d30c46637</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="110" customHeight="1">
+      <c r="A35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">CAUDATE_HTML</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Quantitative MR analysis of caudate abnormalities in pediatric ADHD: Proposal for a diagnostic test</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Quantitative MR analysis of caudate abnormalities in pediatric ADHD_ Proposal for a diagnostic test - ClinicalKey.html</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">0cd65ad2ea1effde97b96ffdb3151aa1e9cbbe66d67029d44eb0e0a024bd1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="110" customHeight="1">
+      <c r="A36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_21117844</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Review of attention-deficit/hyperactivity disorder comorbid with oppositional defiant disorder</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Review of attention-deficit_hyperactivity disorder comorbid with oppositional defiant disorder - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">e751be2e6a9b4100e7f1a40212a6125671c51a59d2404d995579ff1721c80d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="110" customHeight="1">
+      <c r="A37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20410711</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Sex and age differences in attention-deficit/hyperactivity disorder symptoms and diagnoses: implications for DSM-V and ICD-11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Sex and age differences in attention-deficit_hyperactivity disorder symptoms and diagnoses_ implications for DSM-V and ICD-11 - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">2352de9c540b1286611714e6803f7e4a1c24daa87abbf9cd0c94a2fa330340df</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="110" customHeight="1">
+      <c r="A38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20513225</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Stimulant drug effects on attention deficit/hyperactivity disorder: a review of the effects of age and sex of patients</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/Stimulant drug effects on attention deficit_hyperactivity disorder_ a review of the effects of age and sex of patients - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">836a50e43fa44436663a036460b87348c3216234461498a2fcd9f569bc6a129f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="110" customHeight="1">
+      <c r="A39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20839896</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The impact of medications on quality of life in attention-deficit hyperactivity disorder: a systematic review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/The impact of medications on quality of life in attention-deficit hyperactivity disorder_ a systematic review - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">82adf7b51943177cfd8157f1f106ea27247d92e5fc1f95363cf43685ee9bc937</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="110" customHeight="1">
+      <c r="A40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_19482837</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/The presence of attention-deficit hyperactivity disorder (ADHD) and obsessive-compulsive disorder worsen psychosocial and educational problems in Tourette syndrome - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">e2809db8d17b2c5205e0e3ba7e6318737bd7068476739643a4680bf6de6263c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="110" customHeight="1">
+      <c r="A41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20660947</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Event-related potentials associated with error detection in adult ADHD--literature review]</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/[Event-related potentials associated with error detection in adult ADHD--literature review] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">f8ad32fc1353f52d6c6e9abccd9b5079433f23369188c86dcfae3f4fcbe12823</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="110" customHeight="1">
+      <c r="A42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">PMID_20200839</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">[Population-based diagnostic study to compare the DSM-IV and the Questionnaire for screening Latin American schoolchildren and adolescents for attention deficit hyperactivity disorder]</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">../2010 ADHD Papers/[Population-based diagnostic study to compare the DSM-IV and the Questionnaire for screening Latin American schoolchildren and adolescents for attention deficit hyperactivity disorder] - PubMed.html</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">acc200a656cc542f84a8ed744abd54e1287f5b76edcc0b6cb76230b729b5aa23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D25"/>
+  <autoFilter ref="A1:D42"/>
 </worksheet>
 </file>
 
@@ -3486,7 +3953,7 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">2010_8 yo.py, 58 edges, using only the 25 supplied PDF files in 2010 ADHD Papers (24 unique documents; one exact duplicate). Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
+          <t xml:space="preserve">2010_8 yo.py, 58 edges, using 25 supplied PDFs (24 unique PDF documents) and 17 saved HTML article records. Two HTML records reproduce existing PDF studies: 39 unique documents total. Direction, sign, and written reasoning were reviewed; numeric strength was excluded.</t>
         </is>
       </c>
     </row>
@@ -3546,83 +4013,107 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">s12402-010-0036-9 (1).pdf is byte-identical to s12402-010-0036-9.pdf and was counted once as a unique document.</t>
+          <t xml:space="preserve">s12402-010-0036-9 (1).pdf is byte-identical to s12402-010-0036-9.pdf. The sex/age PubMed record (PMID 20410711) and ClinicalKey caudate article reproduce AGE_SEX and CAUDATE_MRI PDFs, respectively. Alternate formats are not independent studies.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="110" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: supported</t>
+          <t xml:space="preserve">html_scope</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
+          <t xml:space="preserve">15 PubMed records and two publisher records were parsed. Only primary article abstracts are used as new evidence; navigation, related articles and saved asset frames are excluded. ClinicalKey also contains the caudate full text, already supplied as PDF. Bipolar publication year is 2010 from the article date and journal citation, despite conflicting website citation metadata. Abstract encoding artifacts are preserved.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="110" customHeight="1">
       <c r="A9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: partially_supported</t>
+          <t xml:space="preserve">evidence_limits</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
+          <t xml:space="preserve">Cross-sectional associations, selected prison/Tourette populations, clinical disparity commentary, and QOL endpoints are distinguished from causal exposure effects. QOL treatment gains do not validate diagnosis-only benefits or adverse-effect-only harm. Pediatric findings are not transferred to adult age-specific claims.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="110" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: contradicted</t>
+          <t xml:space="preserve">Status: supported</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
+          <t xml:space="preserve">Evidence supports the stated direction, sign, and reasoning within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="110" customHeight="1">
       <c r="A11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: mixed_evidence</t>
+          <t xml:space="preserve">Status: partially_supported</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+          <t xml:space="preserve">Evidence supports only part of the claim, a narrower population or outcome, or an association rather than the full causal claim.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="110" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Status: insufficient_evidence</t>
+          <t xml:space="preserve">Status: contradicted</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+          <t xml:space="preserve">Relevant evidence opposes the claimed direction or sign within the declared scope.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
       <c r="A13" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">Status: mixed_evidence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Relevant evidence both supports and opposes the same defined claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="110" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Status: insufficient_evidence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Available evidence does not establish or refute the causal claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
           <t xml:space="preserve">Status: not_assessable</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="0">
+      <c r="B15" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Undefined variable coding or endpoint makes the proposed direction or sign uninterpretable.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B15"/>
 </worksheet>
 </file>